--- a/Test Results/Excel/Summary_Report.xlsx
+++ b/Test Results/Excel/Summary_Report.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify user login with valid email and password credentials</t>
+          <t>Valid Email Password Login Authentication Flow</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify error message on login with invalid password</t>
+          <t>Invalid Password Submission Error Alert Handling</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify error message on login with unregistered email address</t>
+          <t>Unregistered Email Account Rejection Message</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify email input field syntax validation with missing @ domain</t>
+          <t>Email Syntax Validation Rule (@ Domain Filter)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify password masking toggle button reveals plain text password</t>
+          <t>Password Masking Visibility Eye Icon Toggle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify 'Remember Me' checkbox persists session token across browser restart</t>
+          <t>'Remember Me' Session Persistence Across Browser Restart</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify Google OAuth2 single sign-on redirect flow</t>
+          <t>Google OAuth2 Single Sign-On Authentication Redirection</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify GitHub OAuth2 single sign-on authentication callback</t>
+          <t>GitHub OAuth2 Callback Authorization Pipeline</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify password reset request sends verification email link</t>
+          <t>Password Reset Email Verification Link Dispatch</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verify password reset token expiration after 15 minutes</t>
+          <t>Password Reset Token Expiration Lifecycle (15-Min)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verify new password strength meter updates on user input</t>
+          <t>Dynamic Password Strength Indicator Meter Update</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verify user registration form submission with valid details</t>
+          <t>New Account User Registration Form Submission</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verify duplicate email registration returns 409 conflict message</t>
+          <t>Duplicate Account Email Conflict Rejection (409)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verify Terms of Service checkbox mandatory check on signup</t>
+          <t>Mandatory Terms of Service Checkbox Requirement</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Verify Privacy Policy hyperlink opens in new browser tab</t>
+          <t>Privacy Policy External Hyperlink New Tab Launch</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Verify automatic logout after 30 minutes of user inactivity</t>
+          <t>Automatic Session Timeout After 30 Minutes Inactivity</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Verify manual user logout revokes JWT token and redirects to login</t>
+          <t>Manual Logout Revocation of JWT Token</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Verify multi-factor authentication (MFA) OTP prompt display</t>
+          <t>Multi-Factor Authentication (MFA) OTP Input Screen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Verify MFA invalid 6-digit OTP rejection message</t>
+          <t>MFA Invalid 6-Digit OTP Error Rejection</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Verify MFA fallback recovery code verification</t>
+          <t>MFA Backup Recovery Code Verification Sequence</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Verify account lockout after 5 consecutive failed login attempts</t>
+          <t>Account Lockout Enforcement After 5 Failed Logins</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Verify CAPTCHA challenge trigger on suspicious IP login attempt</t>
+          <t>CAPTCHA Challenge Trigger on Suspicious IP Origin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Verify session token refresh API call before expiration</t>
+          <t>JWT Session Bearer Token Auto-Refresh Header</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Verify concurrent login attempt invalidates older session token</t>
+          <t>Concurrent Active Session Invalidation Handling</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Verify XSS injection payload in login email field is sanitized</t>
+          <t>XSS Injection Sanitization in Login Input Fields</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Verify standard user cannot access /admin/dashboard route</t>
+          <t>Standard User Route Access Restriction (/admin)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verify admin user can access system configuration panel</t>
+          <t>Admin Role Access Permission to System Panel</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Verify unauthorized API request returns HTTP 401 Unauthorized status</t>
+          <t>Unauthenticated Request Response Code (401 Unauthorized)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Verify forbidden resource request returns HTTP 403 Forbidden page</t>
+          <t>Forbidden Resource Access Response (403 Forbidden)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Verify role-based action button visibility for Manager role</t>
+          <t>Manager Role Custom Action Button Render</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Verify read-only user cannot submit POST/PUT posture analysis requests</t>
+          <t>Read-Only User Write Operation Rejection (POST/PUT)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Verify user cannot view another user's private posture session history</t>
+          <t>Private Session History Cross-User Access Isolation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Verify tenant isolation in multi-tenant enterprise dashboard</t>
+          <t>Multi-Tenant Enterprise Workspace Data Boundary</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Verify JWT bearer token header validation on protected endpoints</t>
+          <t>JWT Bearer Token Header Injection Verification</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Verify tampered JWT signature is rejected by backend gateway</t>
+          <t>Tampered JWT Cryptographic Signature Rejection</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Verify expired JWT token triggers automatic re-authentication prompt</t>
+          <t>Expired Token Automatic Re-Authentication Dialog</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Verify API key authentication for external posture telemetry ingestion</t>
+          <t>API Key Authentication for Telemetry Ingestion</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Verify revoked API key fails authentication instantly</t>
+          <t>Revoked API Key Gateway Connection Drop</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Verify RBAC permission matrix for posture report deletion</t>
+          <t>RBAC Matrix Enforcement on Posture Record Delete</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Verify CSRF token validation on POST form submissions</t>
+          <t>CSRF Security Token Validation on POST Actions</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify CSRF token validation on POST form submissions' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'CSRF Security Token Validation on POST Actions' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Verify missing authorization header returns proper JSON error body</t>
+          <t>Missing Auth Header JSON Error Schema Output</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Verify session hijacking prevention via IP and User-Agent binding</t>
+          <t>Session Hijacking Prevention via IP/User-Agent Binding</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Verify password change invalidates all existing active sessions</t>
+          <t>Global Session Invalidation on Password Change</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Verify administrative user impersonation audit logging</t>
+          <t>Admin Impersonation Audit Log Event Dispatcher</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Verify privilege escalation payload via URL parameter tampering fails</t>
+          <t>Privilege Escalation Parameter Tampering Block</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Verify browser webcam permission request dialog on calibration page</t>
+          <t>Webcam Browser Permission Dialog Prompt Display</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Verify camera feed preview canvas renders live video frames</t>
+          <t>Live Video Stream HTML5 Canvas Frame Preview</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Verify MediaPipe 33 landmark skeleton overlay renders over live video</t>
+          <t>MediaPipe 33 Landmark Pose Overlay Layer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Verify shoulder alignment baseline angle calculation during setup</t>
+          <t>Shoulder Alignment Baseline Calculation Metric</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verify ear-to-shoulder cervical spine distance measurement calibration</t>
+          <t>Ear-to-Shoulder Cervical Spine Distance Gauge</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verify torso slouch angle threshold slider adjusts sensitivity</t>
+          <t>Slouch Sensitivity Threshold Slider Tuning</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Verify user posture baseline save button updates backend profile</t>
+          <t>Posture Calibration Baseline Profile Update</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Verify webcam disconnection triggers visual reconnect alert banner</t>
+          <t>Webcam Disconnect Reconnection Banner Trigger</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Verify low-light environment warning prompt displays on canvas</t>
+          <t>Low-Ambient Lighting Environment Alert Badge</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Verify multiple person detection warning alert on calibration stream</t>
+          <t>Multiple Pose Detection Warning Banner on Canvas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Verify camera resolution toggle switches between 720p and 1080p</t>
+          <t>Camera Stream Resolution Switcher (720p/1080p)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Verify frame rate monitor displays real-time FPS metric (24-60 FPS)</t>
+          <t>Real-Time FPS Counter Rendering (24-60 FPS)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Verify mirror video view toggle flips video horizontal axis</t>
+          <t>Mirror Video View Horizontal Flip Toggle</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Verify posture calibration wizard step 1 posture position guide</t>
+          <t>Calibration Wizard Step 1 Alignment Guide</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Verify posture calibration wizard step 2 distance from camera check</t>
+          <t>Calibration Wizard Step 2 Camera Distance Check</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Verify posture calibration wizard step 3 side view neck angle test</t>
+          <t>Calibration Wizard Step 3 Neck Angle Measurement</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Verify posture calibration reset button clears previous baseline data</t>
+          <t>Reset Posture Baseline Button Action Handler</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Verify posture score index updates live from 0 to 100 based on posture</t>
+          <t>Live Posture Score Gauge Animation (0-100)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Verify green color indicator ring when posture is within 5% tolerance</t>
+          <t>Green Indicator Ring for Ideal Posture Tolerance</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Verify amber color indicator ring when mild slouching is detected</t>
+          <t>Amber Indicator Ring for Mild Slouch Warning</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Verify red color indicator ring when severe slouching exceeds 15 deg</t>
+          <t>Red Indicator Ring for Severe Slouching Alert</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Verify posture audio chime toggle button silences posture alerts</t>
+          <t>Posture Audio Chime Alert Mute Control</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Verify desktop notification permission prompt on posture slouch alert</t>
+          <t>Desktop Web Push Notification Permission Request</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Verify landmark visibility confidence score threshold filter (&gt;0.8)</t>
+          <t>Landmark Confidence Threshold Filter (&gt;0.80)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Verify camera device selection dropdown switches active webcams</t>
+          <t>Camera Device Dropdown Switcher Selection</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Verify calibration timeout after 3 minutes of uncalibrated video</t>
+          <t>Uncalibrated Video Stream Auto-Timeout (3 Mins)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Verify post-calibration summary modal displays baseline metrics</t>
+          <t>Post-Calibration Summary Modal Metric Render</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Verify posture calibration data export to JSON file</t>
+          <t>Posture Baseline Metric Data Export to JSON</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Verify WebGL hardware acceleration check before MediaPipe init</t>
+          <t>WebGL Hardware Context Check Before Engine Init</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Verify WebRTC video stream failure fallback to periodic image snapshot</t>
+          <t>WebRTC Stream Fallback to Image Snapshot Mode</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Verify WebSocket connection handshake to /ws/posture endpoint</t>
+          <t>WebSocket Handshake Connection to /ws/posture</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Verify live frame landmark coordinates payload structure</t>
+          <t>Live Landmark Coordinate JSON Payload Format</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Verify real-time posture score push updates received every 200ms</t>
+          <t>Real-Time Posture Score Push Updates (200ms Interval)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Verify automatic WebSocket connection heartbeat ping/pong every 30s</t>
+          <t>WebSocket Keep-Alive Ping/Pong Heartbeat Check</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Verify WebSocket reconnection retry backoff strategy on network drop</t>
+          <t>WebSocket Reconnection Exponential Backoff Logic</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Verify live session pause button suspends telemetry transmission</t>
+          <t>Live Tracking Session Pause Button Action</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Verify live session resume button restarts telemetry transmission</t>
+          <t>Live Tracking Session Resume Button Action</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Verify live session stop button finalizes session and saves summary</t>
+          <t>Live Tracking Session Stop and Save Final Summary</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Verify session timer ticker increments continuously during live stream</t>
+          <t>Active Session Clock Timer Increment Ticker</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Verify live slouch counter increments when slouch duration exceeds 5s</t>
+          <t>Slouch Event Counter Trigger on 5s Continuous Slouch</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify live slouch counter increments when slouch duration exceeds 5s' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Slouch Event Counter Trigger on 5s Continuous Slouch' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Verify real-time posture alert sound effect triggers on red status</t>
+          <t>Audio Sound Alert Trigger on Red Posture Status</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Verify browser tab focus change pauses video frame rendering to save CPU</t>
+          <t>Background Tab Inactivity Frame Rendering Throttle</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Verify browser tab refocus resumes video frame rendering seamlessly</t>
+          <t>Foreground Tab Focus Motion Resume Handler</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Verify live telemetry dashboard latency gauge stays below 100ms</t>
+          <t>Telemetry Transmission Latency Gauge (&lt;100ms)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Verify telemetry packet loss recovery handling on dropped frames</t>
+          <t>Packet Loss Recovery Handler for Dropped Frames</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Verify live telemetry data encryption over TLS (WSS protocol)</t>
+          <t>TLS Encryption Security Validation on WSS Protocol</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Verify total posture monitoring active time counter accuracy</t>
+          <t>Total Active Monitoring Counter Precision Test</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Verify peak slouch duration highlight overlay on live timeline</t>
+          <t>Peak Slouch Timestamp Highlighter on Timeline</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Verify real-time neck angle telemetry chart rendering</t>
+          <t>Real-Time Neck Angle Curve Chart Renderer</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Verify real-time shoulder tilt telemetry chart rendering</t>
+          <t>Real-Time Shoulder Tilt Differential Graph</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Verify live session notes input box saves user annotations</t>
+          <t>Live Annotation Session Notes Text Area Save</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Verify posture session goal progress bar updates dynamically</t>
+          <t>Daily Posture Goal Radial Progress Bar Update</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Verify emergency stop button immediately kills webcam stream</t>
+          <t>Emergency Kill-Switch Button Stream Termination</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Verify streaming data bandwidth usage meter under 500 KB/s</t>
+          <t>Bandwidth Data Usage Meter (&lt;500 KB/s Threshold)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Verify live stream error boundary component captures unexpected JS crashes</t>
+          <t>JS Global Error Boundary Handler on Canvas Crash</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Verify daily posture score average KPI card value calculation</t>
+          <t>Daily Posture Score Average KPI Card Calculation</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Verify total slouch incidents KPI card value calculation</t>
+          <t>Total Slouch Incidents Count Metric Display</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Verify active monitoring duration KPI card display in hours/minutes</t>
+          <t>Active Tracking Duration KPI Card (Hours/Mins)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Verify posture health grade badge (A+, A, B, C, F) logic</t>
+          <t>Posture Health Letter Grade Badge Logic (A+ to F)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Verify weekly posture trend line chart renders 7 data points</t>
+          <t>Weekly Posture Trend Line Graph (7-Day Metric)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Verify monthly posture distribution pie chart segment calculations</t>
+          <t>Monthly Posture Distribution Segment Breakdown</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Verify hourly slouch frequency bar chart interactive tooltips</t>
+          <t>Hourly Slouch Frequency Bar Chart Tooltip Interactivity</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Verify posture score vs break frequency scatter plot chart rendering</t>
+          <t>Posture Score vs Rest Break Scatter Plot Render</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Verify date range picker filters analytics between start and end dates</t>
+          <t>Date Range Picker Data Filter Application</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Verify 'Today' quick filter preset sets date filter to current date</t>
+          <t>'Today' Quick Filter Date Preset Action</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Verify 'Last 7 Days' quick filter preset updates dashboard widgets</t>
+          <t>'Last 7 Days' Preset Dashboard Metrics Refresh</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Verify 'Last 30 Days' quick filter preset updates dashboard widgets</t>
+          <t>'Last 30 Days' Preset Dashboard Metrics Refresh</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Verify 'Custom Range' date picker modal input validation</t>
+          <t>Custom Date Picker Input Validation Safeguard</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Verify analytics refresh button reloads latest backend metrics</t>
+          <t>Manual Refresh Button API Re-fetch Trigger</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Verify posture streak widget displays consecutive good posture days</t>
+          <t>Consecutive Good Posture Streak Day Counter</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Verify posture improvement percentage metric comparison with prior week</t>
+          <t>Weekly Posture Improvement Percentage Comparison</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Verify ergonomics tip of the day card rendering</t>
+          <t>Daily Ergonomic Wellness Recommendation Banner</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Verify posture goal progress circular indicator accuracy</t>
+          <t>Target Posture Goal Circular Completion Bar</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Verify worst posture hour of the day highlight alert card</t>
+          <t>Worst Posture Hour Highlight Alert Card</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Verify best posture hour of the day highlight alert card</t>
+          <t>Best Posture Hour Highlight Recognition Card</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Verify posture comparison benchmark with community average</t>
+          <t>Community Posture Score Benchmark Comparison</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Verify dashboard widget drag-and-drop reordering functionality</t>
+          <t>Dashboard Widget Grid Drag-and-Drop Layout</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Verify dashboard widget collapse/expand toggle buttons</t>
+          <t>Dashboard Widget Expand and Collapse Toggle</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Verify posture analytics CSV data export button triggers download</t>
+          <t>Analytics CSV File Data Download Action</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Verify posture analytics Excel data export button triggers download</t>
+          <t>Analytics Excel Workbook Download Action</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Verify dashboard full screen mode button expands view to 100vw</t>
+          <t>Full Screen Mode Viewport Expansion Toggle</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Verify posture health risk advisory alert banner for low scores (&lt;50)</t>
+          <t>Health Risk Advisory Banner for Scores Below 50</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Verify dashboard loading skeleton shimmer state while fetching API</t>
+          <t>Dashboard Loading Skeleton Shimmer State Render</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Verify empty state message on dashboard when no session data exists</t>
+          <t>Empty Dashboard Graphic State for New Accounts</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Verify dashboard chart image export to PNG button</t>
+          <t>Chart Vector Image PNG Export Trigger Button</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify dashboard chart image export to PNG button' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Chart Vector Image PNG Export Trigger Button' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Verify session history data table displays chronologically descending</t>
+          <t>Session History Table Chronological Order Sort</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Verify pagination controls navigate between pages 1, 2, 3...</t>
+          <t>Table Pagination Control Navigation (1, 2, 3...)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Verify page size dropdown switches between 10, 25, 50 rows per page</t>
+          <t>Page Size Dropdown Selection (10, 25, 50 Rows)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Verify search filter input filters sessions by date or session ID</t>
+          <t>Keyword Search Input Filter on Session Records</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Verify sorting session history table by Start Time column ascending/descending</t>
+          <t>Start Time Column Sort Ascending/Descending</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Verify sorting session history table by Posture Score column ascending/descending</t>
+          <t>Posture Score Column Sort Ascending/Descending</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Verify sorting session history table by Duration column ascending/descending</t>
+          <t>Session Duration Column Sort Ascending/Descending</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Verify clicking session row opens detailed session breakdown modal</t>
+          <t>Session Row Click Detailed Modal Drawer Trigger</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Verify session detail modal shows posture score heat map timeline</t>
+          <t>Session Detail Posture Heatmap Timeline View</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Verify session detail modal lists all recorded slouch events with timestamps</t>
+          <t>Session Slouch Log Event Timestamped Breakdown</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Verify session delete button opens confirmation modal</t>
+          <t>Session Deletion Confirmation Prompt Window</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Verify confirming session deletion removes item from table and updates DB</t>
+          <t>Session Delete Execution DB Record Removal</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Verify bulk selection checkboxes select multiple session records</t>
+          <t>Multi-Select Table Checkbox Bulk Action Handler</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Verify bulk delete action removes all selected sessions simultaneously</t>
+          <t>Bulk Delete Batch API Call Processing</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Verify session note editing inline within session history row</t>
+          <t>Inline Session Note Text Editing Capability</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Verify posture session tag filtering (Work, Gaming, Study)</t>
+          <t>Session Tag Category Filter (Work/Gaming/Study)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Verify posture session snapshot image thumbnail preview on hover</t>
+          <t>Posture Snapshot Image Preview Modal Thumbnail</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Verify session duration formatting (e.g. 1h 24m 12s)</t>
+          <t>Formatted Session Duration String Parsing</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Verify session history total record count footer accuracy</t>
+          <t>Session Table Total Record Count Footer Count</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Verify session export to JSON format download</t>
+          <t>Session Raw Metric Export to JSON File Format</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Verify session history table responsive horizontal scroll on mobile viewport</t>
+          <t>Session History Table Mobile Horizontal Scroll</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Verify session history empty search result state display</t>
+          <t>Empty Search Filter Results Placeholder Graphic</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Verify session history network error retry button</t>
+          <t>API Network Error Fetch Retry Action Button</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Verify session history print preview button opens browser print window</t>
+          <t>Table Print Preview Print-Friendly Media View</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Verify session history column customizer checkbox dropdown</t>
+          <t>Column Customization Checkbox Visibility Dropdown</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Verify posture alert settings page renders audio and visual toggles</t>
+          <t>Alert Settings Page Visual Audio Toggle Render</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Verify posture slouch threshold slider (default 15 degrees)</t>
+          <t>Slouch Warning Threshold Slider Configuration</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Verify posture slouch delay alert timer setting (1s to 10s)</t>
+          <t>Slouch Trigger Delay Timer Selector (1s-10s)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Verify audio chime alert volume slider control</t>
+          <t>Alert Volume Master Gain Control Slider</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Verify audio chime tone selection dropdown (Bell, Beep, Chime)</t>
+          <t>Audio Chime Sound Selection Dropdown</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Verify test alert button triggers instant audio sample play</t>
+          <t>Instant Sample Audio Play Test Button</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Verify browser push notification toggle requests browser permission</t>
+          <t>Browser Push Notification Permission Trigger</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Verify email digest notification frequency dropdown (Daily, Weekly, Never)</t>
+          <t>Email Posture Summary Digest Frequency Select</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Verify desktop popup notification on continuous 30-minute slouch</t>
+          <t>30-Minute Continuous Slouch Desktop Popup</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Verify break reminder alert after 45 minutes of continuous sitting</t>
+          <t>45-Minute Continuous Sitting Break Prompt</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Verify ergonomic stretch prompt alert display on break reminder</t>
+          <t>Ergonomic Stretch Routine Modal Display</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Verify alert history log table records all triggered posture warnings</t>
+          <t>Alert History Log Audit Table Generation</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Verify clearing alert history log empties notification storage</t>
+          <t>Clear Alert History Log Purge Button Action</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Verify silent mode toggle disables all sound alerts during meetings</t>
+          <t>Meeting Silent Mode Notification Mute Switch</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Verify scheduled silent mode hours setup (e.g., 12:00 PM - 1:00 PM)</t>
+          <t>Scheduled Quiet Hours Time Range Configuration</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Verify critical posture degradation SMS alert toggle</t>
+          <t>Critical Posture Breakdown SMS Alert Toggle</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Verify alert sound file preloading on app initialization</t>
+          <t>Audio File Asset Preloading on App Launch</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Verify notification badge count increments on new posture report</t>
+          <t>Top Navigation Bar Notification Badge Counter</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Verify clicking notification item redirects to session detail page</t>
+          <t>Notification Item Click Direct Session Reroute</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Verify mark all notifications as read button updates UI badge</t>
+          <t>Mark All Notifications as Read Action Button</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify mark all notifications as read button updates UI badge' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Mark All Notifications as Read Action Button' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Verify drag and drop zone accepts MP4 video files up to 100MB</t>
+          <t>Drag and Drop Upload Zone for 100MB MP4 Files</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Verify file picker button opens native OS file selector dialog</t>
+          <t>File Picker OS Dialog Launch Button Action</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Verify error message when uploading unsupported file format (.txt, .exe)</t>
+          <t>Unsupported Extension (.exe/.txt) Error Block</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Verify error message when uploading video file exceeding 100MB limit</t>
+          <t>File Size Exceeded (&gt;100MB) Rejection Alert</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Verify posture analysis video upload progress bar updates from 0% to 100%</t>
+          <t>Video Upload Percentage Progress Bar Indicator</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Verify video upload cancellation button aborts file upload HTTP request</t>
+          <t>Upload Cancellation HTTP Request Abort Action</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Verify uploaded video frame extraction process status indicator</t>
+          <t>Frame Extraction Progress Status Spinner Screen</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Verify posture analysis processing screen displays MediaPipe processing spinner</t>
+          <t>AI Video Posture Processing Pipeline Indicator</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Verify video posture analysis completion displays detailed AI report</t>
+          <t>Video AI Analysis Report Generation Render</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Verify posture angle timeline overlay rendered under video player</t>
+          <t>Posture Angle Timeline Video Player Overlay</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Verify video playback controls (Play, Pause, Seek, Speed 0.5x-2x)</t>
+          <t>Video Player Playback Speed Controls (0.5x-2x)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Verify video frame-by-frame step forward button during AI review</t>
+          <t>Video Frame Step Forward Precision Controls</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Verify video frame-by-frame step backward button during AI review</t>
+          <t>Video Frame Step Backward Precision Controls</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Verify Cloudinary image upload for user avatar profile picture</t>
+          <t>Cloudinary Profile Avatar Photo Upload Action</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Verify Cloudinary image cropping modal preview before saving avatar</t>
+          <t>Avatar Image Crop Modal Preview and Adjustment</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Verify invalid image file upload rejection on avatar update</t>
+          <t>Corrupted Image File Upload Failure Rejection</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Verify concurrent file upload handling queue (max 3 files)</t>
+          <t>Parallel File Upload Queue Management (Max 3)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Verify server-side malware virus scan validation on uploaded media</t>
+          <t>Server Anti-Virus Security Scan Validation</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Verify automatic video thumbnail generation post-upload</t>
+          <t>Auto Video Keyframe Thumbnail Generation Test</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Verify posture video analysis report export to PDF</t>
+          <t>Video Posture Evaluation PDF Download Button</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Verify uploaded file deletion button purges file from Cloudinary/S3</t>
+          <t>Uploaded Video File Permanent Deletion Action</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Verify video analysis retry button on network transmission failure</t>
+          <t>Network Interruption Upload Retry Action Handler</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Verify video posture summary keyframe highlights gallery display</t>
+          <t>Video Keyframe Highlight Gallery Thumbnail Strip</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Verify video upload bandwidth throttling graceful degraded UX</t>
+          <t>Low Upload Bandwidth Degradation Graceful Mode</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Verify uploaded video aspect ratio preservation in HTML5 video tag</t>
+          <t>Aspect Ratio Preservation in HTML5 Video Tag</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Verify PDF posture evaluation report layout and header formatting</t>
+          <t>PDF Posture Evaluation Report Layout Structure</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Verify PDF report includes user name, date range, and posture grade</t>
+          <t>PDF Report Header User Identity Metadata Render</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Verify PDF report embedded posture score trend chart image quality</t>
+          <t>PDF Report Embedded Trend Chart Image Clarity</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Verify PDF report ergonomic recommendations summary section</t>
+          <t>PDF Ergonomic Recommendation Summary Section</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Verify Excel raw posture telemetry export contains all 33 landmark columns</t>
+          <t>Excel 33 Pose Landmark Raw Coordinates Export</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Verify Excel report includes multi-sheet tabs for Sessions, Summary, and Errors</t>
+          <t>Excel Workbook Multi-Sheet Tab Schema Structure</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Verify CSV export file formatting with comma separation and UTF-8 encoding</t>
+          <t>CSV UTF-8 Formatted Data File Dispatch Action</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Verify posture report email delivery feature sends PDF attachment</t>
+          <t>PDF Posture Report Email Delivery Dispatch</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Verify custom date range filter applies to exported report data</t>
+          <t>Date Range Filter Application on Exported Data</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Verify automated weekly posture summary report email scheduling</t>
+          <t>Weekly Automated Email Report Schedule Setup</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Verify automated monthly posture summary report email scheduling</t>
+          <t>Monthly Automated Email Report Schedule Setup</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Verify report generation loading overlay during PDF rendering</t>
+          <t>Report PDF Generation Rendering Loading Overlay</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Verify print stylesheet (@media print) formats report page cleanly</t>
+          <t>@media print Print Stylesheet Layout Optimizer</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Verify posture health certificate download feature</t>
+          <t>Posture Health Certification PDF Certificate</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Verify posture data anonymized export for medical study consent</t>
+          <t>Anonymized Posture Medical Consent Export Action</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Verify report download failure retry prompt display</t>
+          <t>Report Download Error Retry Action Button Prompt</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Verify password-protected PDF report export security option</t>
+          <t>Password-Encrypted PDF Report Protection Toggle</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Verify corporate team posture aggregation report export for admins</t>
+          <t>Corporate Team Aggregated Posture Admin Report</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Verify export filename includes timestamp (e.g., Posture_Report_20260805.pdf)</t>
+          <t>Report Filename Timestamp Generator Syntax</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Verify report preview modal displays accurate multi-page preview</t>
+          <t>Multi-Page Report Preview Dialog Modal Render</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify report preview modal displays accurate multi-page preview' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Multi-Page Report Preview Dialog Modal Render' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Verify top navigation bar links (Home, Calibration, Analytics, Reports, Settings)</t>
+          <t>Top Navbar Primary Destinations Routing Test</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Verify active page route link highlighting in navbar</t>
+          <t>Active Page Link CSS State Highlight Visual</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Verify sidebar toggle button expands and collapses side menu panel</t>
+          <t>Sidebar Collapsible Panel Toggle Button Action</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Verify sidebar navigation links match top navbar destinations</t>
+          <t>Sidebar Navigation Link Destination Matching</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Verify browser back button returns to previously visited route</t>
+          <t>Browser History Back Button Route Reversion</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Verify browser forward button navigates ahead correctly</t>
+          <t>Browser History Forward Navigation Flow Test</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Verify browser page refresh (F5) maintains current URL state and session</t>
+          <t>Page Refresh (F5) URL State and Session Retention</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Verify 404 Page Not Found rendering for non-existent URL routes</t>
+          <t>404 Page Not Found Route Fallback Display</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Verify 404 page 'Return to Home' CTA button functionality</t>
+          <t>404 Page 'Return to Dashboard' Button Redirect</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Verify breadcrumbs trail updating dynamically per nested sub-route</t>
+          <t>Dynamic Breadcrumbs Trail Update per Sub-Route</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Verify footer quick links (About, Terms, Privacy, Support, API Docs)</t>
+          <t>Footer Terms and Privacy Policy Hyperlinks</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Verify sticky navigation bar remains pinned to top on page scroll</t>
+          <t>Sticky Navigation Bar Scroll Pinning Behavior</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Verify user profile dropdown menu opens on avatar click</t>
+          <t>User Profile Avatar Header Menu Dropdown Open</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Verify user profile dropdown items (Profile, Billing, Settings, Logout)</t>
+          <t>Profile Dropdown Menu Option Redirects Test</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Verify keyboard shortcut 'G+D' navigates to Dashboard</t>
+          <t>Keyboard Shortcut 'G+D' Dashboard Navigation</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Verify keyboard shortcut 'G+C' navigates to Calibration</t>
+          <t>Keyboard Shortcut 'G+C' Calibration Navigation</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Verify modal dialog close button (X) dismisses overlay</t>
+          <t>Modal Close Button (X) Click Dismiss Action</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Verify pressing ESC key closes open modal dialogs</t>
+          <t>Escape Key Press Modal Window Dismissal</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Verify clicking outside modal backdrop dismisses overlay</t>
+          <t>Backdrop Click Modal Dismissal Behavior Test</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Verify page title (&lt;title&gt; tag) updates dynamically per route</t>
+          <t>Dynamic Page Document Title (&lt;title&gt;) Updates</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Verify dark mode theme toggle switches CSS background and text variables</t>
+          <t>Dark Theme Palette Variable CSS Class Switch</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Verify light mode theme toggle restores original high-contrast theme</t>
+          <t>Light Theme High-Contrast Mode Color Restoration</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Verify system color scheme preference (prefers-color-scheme) auto-detection</t>
+          <t>System Prefers-Color-Scheme Auto Detection</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Verify persistent theme preference saved in browser localStorage</t>
+          <t>Theme Preference Persistence in localStorage</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Verify high contrast mode toggle for visually impaired users</t>
+          <t>High Contrast Accessibility Toggle Switch</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Verify font size scaling controls (Small, Medium, Large, Extra Large)</t>
+          <t>Typography Font Size Scaling (Small to XL)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Verify screen reader ARIA labels on all interactive buttons</t>
+          <t>Interactive Component Screen Reader ARIA Labels</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Verify ARIA live regions announce posture status changes</t>
+          <t>ARIA Live Region Speech Output on Alert Push</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Verify keyboard focus indicator outline visible on TAB navigation</t>
+          <t>Keyboard TAB Focus Outline Indicator Highlight</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Verify tab order traverses web page elements in logical reading sequence</t>
+          <t>Logical TAB Key Navigation Order Sequence</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Verify color contrast ratio meets WCAG 2.1 AA benchmark (4.5:1 ratio)</t>
+          <t>WCAG 2.1 AA Color Contrast Ratio Verification</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Verify form input fields have explicit associated &lt;label&gt; elements</t>
+          <t>Form Input Field Associated &lt;label&gt; Tag Check</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Verify decorative images have empty alt text (alt='')</t>
+          <t>Decorative Image Empty Alt Text (alt='') Rule</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Verify functional images have descriptive alt text</t>
+          <t>Functional Icon Graphic Descriptive Alt Text</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Verify skipping to main content link works for screen readers</t>
+          <t>'Skip to Main Content' Accessibility Link Test</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Verify interface animations pause when prefers-reduced-motion is active</t>
+          <t>Prefers-Reduced-Motion CSS Transition Freeze</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Verify tooltips accessible via keyboard focus hover</t>
+          <t>Keyboard Focus Hover Tooltip Popover Action</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Verify error state text is not conveyed by color alone (includes icons)</t>
+          <t>Multi-Sensory Error State Display (Icon plus Text)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Verify language attribute (&lt;html lang='en'&gt;) defined on document root</t>
+          <t>Document Root Language Attribute (&lt;html lang='en'&gt;)</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Verify semantic HTML5 tags (&lt;header&gt;, &lt;main&gt;, &lt;nav&gt;, &lt;footer&gt;) used throughout</t>
+          <t>Semantic HTML5 Structural Tags Layout Integrity</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Verify user profile name field trims leading and trailing whitespace</t>
+          <t>User Profile Display Name Whitespace Trimming</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Verify user profile name field max length restriction (50 chars)</t>
+          <t>Profile Display Name Character Cap (50 Chars)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Verify special character handling in user profile display name</t>
+          <t>Special Character Encoding in User Display Name</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Verify email input field auto-complete attribute enabled</t>
+          <t>Email Address Field Browser Autocomplete Attribute</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Verify phone number field enforces international E.164 format (+1234567890)</t>
+          <t>E.164 International Phone Format Validation</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify phone number field enforces international E.164 format (+1234567890)' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'E.164 International Phone Format Validation' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Verify birthdate date picker restricts selection of future dates</t>
+          <t>Birthdate Selection Future Date Rejection Rule</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Verify height/weight numeric input fields reject negative numbers</t>
+          <t>Height and Weight Input Field Negative Number Rejection</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Verify height metric (cm) vs imperial (inches) unit toggle calculation</t>
+          <t>Height Units Switcher (Centimeters vs Inches)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Verify weight metric (kg) vs imperial (lbs) unit toggle calculation</t>
+          <t>Weight Units Switcher (Kilograms vs Pounds)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Verify posture target daily goal input field (range 15 to 480 mins)</t>
+          <t>Daily Posture Target Goal Range (15-480 Mins)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Verify real-time inline validation error display on blur event</t>
+          <t>Inline Real-Time Input Error Blur Validation</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Verify submit button disabled until all mandatory form fields are valid</t>
+          <t>Submit Button Disabled State on Invalid Inputs</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Verify clearing form button resets input fields to default values</t>
+          <t>Form Reset Clear Button Default State Restore</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Verify unsaved form changes warning modal on navigating away</t>
+          <t>Unsaved Form Changes Warning Navigation Alert</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Verify HTML form submission triggers on pressing Enter key inside text input</t>
+          <t>Enter Key Press Form Submission Event Launch</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Verify text area character counter updates live as user types</t>
+          <t>Textarea Live Remaining Character Counter</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Verify password confirmation field matches new password input</t>
+          <t>Password Confirmation Match Validation Check</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Verify SQL injection string in input field is escaped properly</t>
+          <t>Input Escaping Security against SQL Injection</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Verify HTML code snippet input is escaped to prevent XSS execution</t>
+          <t>HTML Tag Encoding Security against XSS Payloads</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Verify form submission double-click prevention disables submit button</t>
+          <t>Submit Button Double-Click Action Prevention</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Verify desktop layout rendering at 1920x1080 resolution</t>
+          <t>1920x1080 Full HD Monitor Viewport Layout</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Verify laptop layout rendering at 1366x768 resolution</t>
+          <t>1366x768 Standard Laptop Monitor Viewport Layout</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Verify tablet viewport rendering at 768x1024 portrait resolution</t>
+          <t>768x1024 Tablet Portrait Mode Viewport Layout</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Verify mobile viewport rendering at 375x812 iPhone X resolution</t>
+          <t>375x812 iPhone Mobile Screen Viewport Layout</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Verify hamburger menu appears on screens below 768px width</t>
+          <t>Mobile Viewport Hamburger Navigation Menu Appears</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Verify navigation menu collapses into slide-over drawer on mobile</t>
+          <t>Mobile Side-Drawer Navigation Transition</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Verify dashboard analytics grid wraps from 4 columns to 1 column on mobile</t>
+          <t>Dashboard 4-Column Grid Collapse to 1-Column</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Verify live video stream canvas scales proportionally to screen width</t>
+          <t>Webcam Live Canvas Fluid Width Resizing</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Verify data tables horizontal scrollbar display on small viewports</t>
+          <t>Data Table Horizontal Scroll Bar Mobile Rendering</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Verify font size scaling dynamically across desktop, tablet, and mobile breakpoints</t>
+          <t>Fluid Typography Clamp Font Size Scaling</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify font size scaling dynamically across desktop, tablet, and mobile breakpoints' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Fluid Typography Clamp Font Size Scaling' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Verify touch drag gestures supported on mobile charts slider</t>
+          <t>Touch Screen Drag Gesture Support on Charts</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Verify Chrome browser latest version rendering stability</t>
+          <t>Google Chrome Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Verify Firefox browser latest version rendering stability</t>
+          <t>Mozilla Firefox Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Verify Safari browser latest version rendering stability</t>
+          <t>Apple Safari Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Verify Microsoft Edge browser latest version rendering stability</t>
+          <t>Microsoft Edge Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Verify MediaPipe WASM module loading across Chromium and WebKit browsers</t>
+          <t>MediaPipe WASM Engine Cross-Browser Loading</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Verify WebGL 2.0 context initialization fallback on legacy hardware</t>
+          <t>WebGL Context Initialization Hardware Fallback</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Verify high DPI Retina display crisp image rendering</t>
+          <t>High DPI Retina Display Image Sharpness Check</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Verify viewport meta tag (width=device-width, initial-scale=1.0) present</t>
+          <t>Viewport Meta Tag Initial Scale Configuration</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Verify page content does not cause unintended horizontal overflow</t>
+          <t>Zero Horizontal Page Overflow Layout Inspection</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Verify CSS grid and flexbox layout stability across browser engines</t>
+          <t>CSS Grid and Flexbox Layout Engine Parity</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Verify touch target minimum size of 44x44 pixels on mobile viewports</t>
+          <t>Minimum 44x44px Touch Target Size Verification</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Verify smooth CSS transition animations at 60 FPS</t>
+          <t>CSS Smooth Transition Animation 60 FPS Check</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Verify print CSS media query removes background images and navigation bars</t>
+          <t>@media print Navigation and Header Masking</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Verify web app manifest (manifest.json) PWA installability prompt</t>
+          <t>Web App Manifest PWA Installability Prompt</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify user login with valid email and password credentials</t>
+          <t>Valid Email Password Login Authentication Flow</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify error message on login with invalid password</t>
+          <t>Invalid Password Submission Error Alert Handling</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify error message on login with unregistered email address</t>
+          <t>Unregistered Email Account Rejection Message</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify email input field syntax validation with missing @ domain</t>
+          <t>Email Syntax Validation Rule (@ Domain Filter)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify password masking toggle button reveals plain text password</t>
+          <t>Password Masking Visibility Eye Icon Toggle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify 'Remember Me' checkbox persists session token across browser restart</t>
+          <t>'Remember Me' Session Persistence Across Browser Restart</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify Google OAuth2 single sign-on redirect flow</t>
+          <t>Google OAuth2 Single Sign-On Authentication Redirection</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify GitHub OAuth2 single sign-on authentication callback</t>
+          <t>GitHub OAuth2 Callback Authorization Pipeline</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify password reset request sends verification email link</t>
+          <t>Password Reset Email Verification Link Dispatch</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verify password reset token expiration after 15 minutes</t>
+          <t>Password Reset Token Expiration Lifecycle (15-Min)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verify new password strength meter updates on user input</t>
+          <t>Dynamic Password Strength Indicator Meter Update</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verify user registration form submission with valid details</t>
+          <t>New Account User Registration Form Submission</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verify duplicate email registration returns 409 conflict message</t>
+          <t>Duplicate Account Email Conflict Rejection (409)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verify Terms of Service checkbox mandatory check on signup</t>
+          <t>Mandatory Terms of Service Checkbox Requirement</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Verify Privacy Policy hyperlink opens in new browser tab</t>
+          <t>Privacy Policy External Hyperlink New Tab Launch</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Verify automatic logout after 30 minutes of user inactivity</t>
+          <t>Automatic Session Timeout After 30 Minutes Inactivity</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Verify manual user logout revokes JWT token and redirects to login</t>
+          <t>Manual Logout Revocation of JWT Token</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Verify multi-factor authentication (MFA) OTP prompt display</t>
+          <t>Multi-Factor Authentication (MFA) OTP Input Screen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Verify MFA invalid 6-digit OTP rejection message</t>
+          <t>MFA Invalid 6-Digit OTP Error Rejection</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Verify MFA fallback recovery code verification</t>
+          <t>MFA Backup Recovery Code Verification Sequence</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Verify account lockout after 5 consecutive failed login attempts</t>
+          <t>Account Lockout Enforcement After 5 Failed Logins</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Verify CAPTCHA challenge trigger on suspicious IP login attempt</t>
+          <t>CAPTCHA Challenge Trigger on Suspicious IP Origin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Verify session token refresh API call before expiration</t>
+          <t>JWT Session Bearer Token Auto-Refresh Header</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Verify concurrent login attempt invalidates older session token</t>
+          <t>Concurrent Active Session Invalidation Handling</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Verify XSS injection payload in login email field is sanitized</t>
+          <t>XSS Injection Sanitization in Login Input Fields</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Verify standard user cannot access /admin/dashboard route</t>
+          <t>Standard User Route Access Restriction (/admin)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verify admin user can access system configuration panel</t>
+          <t>Admin Role Access Permission to System Panel</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Verify unauthorized API request returns HTTP 401 Unauthorized status</t>
+          <t>Unauthenticated Request Response Code (401 Unauthorized)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Verify forbidden resource request returns HTTP 403 Forbidden page</t>
+          <t>Forbidden Resource Access Response (403 Forbidden)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Verify role-based action button visibility for Manager role</t>
+          <t>Manager Role Custom Action Button Render</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Verify read-only user cannot submit POST/PUT posture analysis requests</t>
+          <t>Read-Only User Write Operation Rejection (POST/PUT)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Verify user cannot view another user's private posture session history</t>
+          <t>Private Session History Cross-User Access Isolation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Verify tenant isolation in multi-tenant enterprise dashboard</t>
+          <t>Multi-Tenant Enterprise Workspace Data Boundary</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Verify JWT bearer token header validation on protected endpoints</t>
+          <t>JWT Bearer Token Header Injection Verification</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Verify tampered JWT signature is rejected by backend gateway</t>
+          <t>Tampered JWT Cryptographic Signature Rejection</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Verify expired JWT token triggers automatic re-authentication prompt</t>
+          <t>Expired Token Automatic Re-Authentication Dialog</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Verify API key authentication for external posture telemetry ingestion</t>
+          <t>API Key Authentication for Telemetry Ingestion</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Verify revoked API key fails authentication instantly</t>
+          <t>Revoked API Key Gateway Connection Drop</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Verify RBAC permission matrix for posture report deletion</t>
+          <t>RBAC Matrix Enforcement on Posture Record Delete</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Verify missing authorization header returns proper JSON error body</t>
+          <t>Missing Auth Header JSON Error Schema Output</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Verify session hijacking prevention via IP and User-Agent binding</t>
+          <t>Session Hijacking Prevention via IP/User-Agent Binding</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Verify password change invalidates all existing active sessions</t>
+          <t>Global Session Invalidation on Password Change</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Verify administrative user impersonation audit logging</t>
+          <t>Admin Impersonation Audit Log Event Dispatcher</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Verify privilege escalation payload via URL parameter tampering fails</t>
+          <t>Privilege Escalation Parameter Tampering Block</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Verify browser webcam permission request dialog on calibration page</t>
+          <t>Webcam Browser Permission Dialog Prompt Display</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Verify camera feed preview canvas renders live video frames</t>
+          <t>Live Video Stream HTML5 Canvas Frame Preview</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Verify MediaPipe 33 landmark skeleton overlay renders over live video</t>
+          <t>MediaPipe 33 Landmark Pose Overlay Layer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Verify shoulder alignment baseline angle calculation during setup</t>
+          <t>Shoulder Alignment Baseline Calculation Metric</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Verify ear-to-shoulder cervical spine distance measurement calibration</t>
+          <t>Ear-to-Shoulder Cervical Spine Distance Gauge</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verify torso slouch angle threshold slider adjusts sensitivity</t>
+          <t>Slouch Sensitivity Threshold Slider Tuning</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verify user posture baseline save button updates backend profile</t>
+          <t>Posture Calibration Baseline Profile Update</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Verify webcam disconnection triggers visual reconnect alert banner</t>
+          <t>Webcam Disconnect Reconnection Banner Trigger</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Verify low-light environment warning prompt displays on canvas</t>
+          <t>Low-Ambient Lighting Environment Alert Badge</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Verify multiple person detection warning alert on calibration stream</t>
+          <t>Multiple Pose Detection Warning Banner on Canvas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Verify camera resolution toggle switches between 720p and 1080p</t>
+          <t>Camera Stream Resolution Switcher (720p/1080p)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Verify frame rate monitor displays real-time FPS metric (24-60 FPS)</t>
+          <t>Real-Time FPS Counter Rendering (24-60 FPS)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Verify mirror video view toggle flips video horizontal axis</t>
+          <t>Mirror Video View Horizontal Flip Toggle</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Verify posture calibration wizard step 1 posture position guide</t>
+          <t>Calibration Wizard Step 1 Alignment Guide</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Verify posture calibration wizard step 2 distance from camera check</t>
+          <t>Calibration Wizard Step 2 Camera Distance Check</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Verify posture calibration wizard step 3 side view neck angle test</t>
+          <t>Calibration Wizard Step 3 Neck Angle Measurement</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Verify posture calibration reset button clears previous baseline data</t>
+          <t>Reset Posture Baseline Button Action Handler</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Verify posture score index updates live from 0 to 100 based on posture</t>
+          <t>Live Posture Score Gauge Animation (0-100)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Verify green color indicator ring when posture is within 5% tolerance</t>
+          <t>Green Indicator Ring for Ideal Posture Tolerance</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Verify amber color indicator ring when mild slouching is detected</t>
+          <t>Amber Indicator Ring for Mild Slouch Warning</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Verify red color indicator ring when severe slouching exceeds 15 deg</t>
+          <t>Red Indicator Ring for Severe Slouching Alert</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Verify posture audio chime toggle button silences posture alerts</t>
+          <t>Posture Audio Chime Alert Mute Control</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Verify desktop notification permission prompt on posture slouch alert</t>
+          <t>Desktop Web Push Notification Permission Request</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Verify landmark visibility confidence score threshold filter (&gt;0.8)</t>
+          <t>Landmark Confidence Threshold Filter (&gt;0.80)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Verify camera device selection dropdown switches active webcams</t>
+          <t>Camera Device Dropdown Switcher Selection</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Verify calibration timeout after 3 minutes of uncalibrated video</t>
+          <t>Uncalibrated Video Stream Auto-Timeout (3 Mins)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Verify post-calibration summary modal displays baseline metrics</t>
+          <t>Post-Calibration Summary Modal Metric Render</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Verify posture calibration data export to JSON file</t>
+          <t>Posture Baseline Metric Data Export to JSON</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Verify WebGL hardware acceleration check before MediaPipe init</t>
+          <t>WebGL Hardware Context Check Before Engine Init</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Verify WebRTC video stream failure fallback to periodic image snapshot</t>
+          <t>WebRTC Stream Fallback to Image Snapshot Mode</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Verify WebSocket connection handshake to /ws/posture endpoint</t>
+          <t>WebSocket Handshake Connection to /ws/posture</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Verify live frame landmark coordinates payload structure</t>
+          <t>Live Landmark Coordinate JSON Payload Format</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Verify real-time posture score push updates received every 200ms</t>
+          <t>Real-Time Posture Score Push Updates (200ms Interval)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Verify automatic WebSocket connection heartbeat ping/pong every 30s</t>
+          <t>WebSocket Keep-Alive Ping/Pong Heartbeat Check</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Verify WebSocket reconnection retry backoff strategy on network drop</t>
+          <t>WebSocket Reconnection Exponential Backoff Logic</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Verify live session pause button suspends telemetry transmission</t>
+          <t>Live Tracking Session Pause Button Action</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Verify live session resume button restarts telemetry transmission</t>
+          <t>Live Tracking Session Resume Button Action</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Verify live session stop button finalizes session and saves summary</t>
+          <t>Live Tracking Session Stop and Save Final Summary</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Verify session timer ticker increments continuously during live stream</t>
+          <t>Active Session Clock Timer Increment Ticker</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Verify real-time posture alert sound effect triggers on red status</t>
+          <t>Audio Sound Alert Trigger on Red Posture Status</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Verify browser tab focus change pauses video frame rendering to save CPU</t>
+          <t>Background Tab Inactivity Frame Rendering Throttle</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Verify browser tab refocus resumes video frame rendering seamlessly</t>
+          <t>Foreground Tab Focus Motion Resume Handler</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Verify live telemetry dashboard latency gauge stays below 100ms</t>
+          <t>Telemetry Transmission Latency Gauge (&lt;100ms)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Verify telemetry packet loss recovery handling on dropped frames</t>
+          <t>Packet Loss Recovery Handler for Dropped Frames</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Verify live telemetry data encryption over TLS (WSS protocol)</t>
+          <t>TLS Encryption Security Validation on WSS Protocol</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Verify total posture monitoring active time counter accuracy</t>
+          <t>Total Active Monitoring Counter Precision Test</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Verify peak slouch duration highlight overlay on live timeline</t>
+          <t>Peak Slouch Timestamp Highlighter on Timeline</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Verify real-time neck angle telemetry chart rendering</t>
+          <t>Real-Time Neck Angle Curve Chart Renderer</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Verify real-time shoulder tilt telemetry chart rendering</t>
+          <t>Real-Time Shoulder Tilt Differential Graph</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Verify live session notes input box saves user annotations</t>
+          <t>Live Annotation Session Notes Text Area Save</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Verify posture session goal progress bar updates dynamically</t>
+          <t>Daily Posture Goal Radial Progress Bar Update</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Verify emergency stop button immediately kills webcam stream</t>
+          <t>Emergency Kill-Switch Button Stream Termination</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Verify streaming data bandwidth usage meter under 500 KB/s</t>
+          <t>Bandwidth Data Usage Meter (&lt;500 KB/s Threshold)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Verify live stream error boundary component captures unexpected JS crashes</t>
+          <t>JS Global Error Boundary Handler on Canvas Crash</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Verify daily posture score average KPI card value calculation</t>
+          <t>Daily Posture Score Average KPI Card Calculation</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Verify total slouch incidents KPI card value calculation</t>
+          <t>Total Slouch Incidents Count Metric Display</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Verify active monitoring duration KPI card display in hours/minutes</t>
+          <t>Active Tracking Duration KPI Card (Hours/Mins)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Verify posture health grade badge (A+, A, B, C, F) logic</t>
+          <t>Posture Health Letter Grade Badge Logic (A+ to F)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Verify weekly posture trend line chart renders 7 data points</t>
+          <t>Weekly Posture Trend Line Graph (7-Day Metric)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Verify monthly posture distribution pie chart segment calculations</t>
+          <t>Monthly Posture Distribution Segment Breakdown</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Verify hourly slouch frequency bar chart interactive tooltips</t>
+          <t>Hourly Slouch Frequency Bar Chart Tooltip Interactivity</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Verify posture score vs break frequency scatter plot chart rendering</t>
+          <t>Posture Score vs Rest Break Scatter Plot Render</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Verify date range picker filters analytics between start and end dates</t>
+          <t>Date Range Picker Data Filter Application</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Verify 'Today' quick filter preset sets date filter to current date</t>
+          <t>'Today' Quick Filter Date Preset Action</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Verify 'Last 7 Days' quick filter preset updates dashboard widgets</t>
+          <t>'Last 7 Days' Preset Dashboard Metrics Refresh</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Verify 'Last 30 Days' quick filter preset updates dashboard widgets</t>
+          <t>'Last 30 Days' Preset Dashboard Metrics Refresh</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Verify 'Custom Range' date picker modal input validation</t>
+          <t>Custom Date Picker Input Validation Safeguard</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Verify analytics refresh button reloads latest backend metrics</t>
+          <t>Manual Refresh Button API Re-fetch Trigger</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Verify posture streak widget displays consecutive good posture days</t>
+          <t>Consecutive Good Posture Streak Day Counter</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Verify posture improvement percentage metric comparison with prior week</t>
+          <t>Weekly Posture Improvement Percentage Comparison</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Verify ergonomics tip of the day card rendering</t>
+          <t>Daily Ergonomic Wellness Recommendation Banner</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Verify posture goal progress circular indicator accuracy</t>
+          <t>Target Posture Goal Circular Completion Bar</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Verify worst posture hour of the day highlight alert card</t>
+          <t>Worst Posture Hour Highlight Alert Card</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Verify best posture hour of the day highlight alert card</t>
+          <t>Best Posture Hour Highlight Recognition Card</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Verify posture comparison benchmark with community average</t>
+          <t>Community Posture Score Benchmark Comparison</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Verify dashboard widget drag-and-drop reordering functionality</t>
+          <t>Dashboard Widget Grid Drag-and-Drop Layout</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Verify dashboard widget collapse/expand toggle buttons</t>
+          <t>Dashboard Widget Expand and Collapse Toggle</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Verify posture analytics CSV data export button triggers download</t>
+          <t>Analytics CSV File Data Download Action</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Verify posture analytics Excel data export button triggers download</t>
+          <t>Analytics Excel Workbook Download Action</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Verify dashboard full screen mode button expands view to 100vw</t>
+          <t>Full Screen Mode Viewport Expansion Toggle</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Verify posture health risk advisory alert banner for low scores (&lt;50)</t>
+          <t>Health Risk Advisory Banner for Scores Below 50</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Verify dashboard loading skeleton shimmer state while fetching API</t>
+          <t>Dashboard Loading Skeleton Shimmer State Render</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Verify empty state message on dashboard when no session data exists</t>
+          <t>Empty Dashboard Graphic State for New Accounts</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Verify session history data table displays chronologically descending</t>
+          <t>Session History Table Chronological Order Sort</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Verify pagination controls navigate between pages 1, 2, 3...</t>
+          <t>Table Pagination Control Navigation (1, 2, 3...)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Verify page size dropdown switches between 10, 25, 50 rows per page</t>
+          <t>Page Size Dropdown Selection (10, 25, 50 Rows)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Verify search filter input filters sessions by date or session ID</t>
+          <t>Keyword Search Input Filter on Session Records</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Verify sorting session history table by Start Time column ascending/descending</t>
+          <t>Start Time Column Sort Ascending/Descending</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Verify sorting session history table by Posture Score column ascending/descending</t>
+          <t>Posture Score Column Sort Ascending/Descending</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Verify sorting session history table by Duration column ascending/descending</t>
+          <t>Session Duration Column Sort Ascending/Descending</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Verify clicking session row opens detailed session breakdown modal</t>
+          <t>Session Row Click Detailed Modal Drawer Trigger</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Verify session detail modal shows posture score heat map timeline</t>
+          <t>Session Detail Posture Heatmap Timeline View</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Verify session detail modal lists all recorded slouch events with timestamps</t>
+          <t>Session Slouch Log Event Timestamped Breakdown</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Verify session delete button opens confirmation modal</t>
+          <t>Session Deletion Confirmation Prompt Window</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Verify confirming session deletion removes item from table and updates DB</t>
+          <t>Session Delete Execution DB Record Removal</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Verify bulk selection checkboxes select multiple session records</t>
+          <t>Multi-Select Table Checkbox Bulk Action Handler</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Verify bulk delete action removes all selected sessions simultaneously</t>
+          <t>Bulk Delete Batch API Call Processing</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Verify session note editing inline within session history row</t>
+          <t>Inline Session Note Text Editing Capability</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Verify posture session tag filtering (Work, Gaming, Study)</t>
+          <t>Session Tag Category Filter (Work/Gaming/Study)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Verify posture session snapshot image thumbnail preview on hover</t>
+          <t>Posture Snapshot Image Preview Modal Thumbnail</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Verify session duration formatting (e.g. 1h 24m 12s)</t>
+          <t>Formatted Session Duration String Parsing</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Verify session history total record count footer accuracy</t>
+          <t>Session Table Total Record Count Footer Count</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Verify session export to JSON format download</t>
+          <t>Session Raw Metric Export to JSON File Format</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Verify session history table responsive horizontal scroll on mobile viewport</t>
+          <t>Session History Table Mobile Horizontal Scroll</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -15359,7 +15359,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Verify session history empty search result state display</t>
+          <t>Empty Search Filter Results Placeholder Graphic</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Verify session history network error retry button</t>
+          <t>API Network Error Fetch Retry Action Button</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Verify session history print preview button opens browser print window</t>
+          <t>Table Print Preview Print-Friendly Media View</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Verify session history column customizer checkbox dropdown</t>
+          <t>Column Customization Checkbox Visibility Dropdown</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -15487,7 +15487,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Verify posture alert settings page renders audio and visual toggles</t>
+          <t>Alert Settings Page Visual Audio Toggle Render</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Verify posture slouch threshold slider (default 15 degrees)</t>
+          <t>Slouch Warning Threshold Slider Configuration</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Verify posture slouch delay alert timer setting (1s to 10s)</t>
+          <t>Slouch Trigger Delay Timer Selector (1s-10s)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Verify audio chime alert volume slider control</t>
+          <t>Alert Volume Master Gain Control Slider</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Verify audio chime tone selection dropdown (Bell, Beep, Chime)</t>
+          <t>Audio Chime Sound Selection Dropdown</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Verify test alert button triggers instant audio sample play</t>
+          <t>Instant Sample Audio Play Test Button</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Verify browser push notification toggle requests browser permission</t>
+          <t>Browser Push Notification Permission Trigger</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Verify email digest notification frequency dropdown (Daily, Weekly, Never)</t>
+          <t>Email Posture Summary Digest Frequency Select</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Verify desktop popup notification on continuous 30-minute slouch</t>
+          <t>30-Minute Continuous Slouch Desktop Popup</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Verify break reminder alert after 45 minutes of continuous sitting</t>
+          <t>45-Minute Continuous Sitting Break Prompt</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Verify ergonomic stretch prompt alert display on break reminder</t>
+          <t>Ergonomic Stretch Routine Modal Display</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Verify alert history log table records all triggered posture warnings</t>
+          <t>Alert History Log Audit Table Generation</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Verify clearing alert history log empties notification storage</t>
+          <t>Clear Alert History Log Purge Button Action</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Verify silent mode toggle disables all sound alerts during meetings</t>
+          <t>Meeting Silent Mode Notification Mute Switch</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Verify scheduled silent mode hours setup (e.g., 12:00 PM - 1:00 PM)</t>
+          <t>Scheduled Quiet Hours Time Range Configuration</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Verify critical posture degradation SMS alert toggle</t>
+          <t>Critical Posture Breakdown SMS Alert Toggle</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Verify alert sound file preloading on app initialization</t>
+          <t>Audio File Asset Preloading on App Launch</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Verify notification badge count increments on new posture report</t>
+          <t>Top Navigation Bar Notification Badge Counter</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Verify clicking notification item redirects to session detail page</t>
+          <t>Notification Item Click Direct Session Reroute</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Verify drag and drop zone accepts MP4 video files up to 100MB</t>
+          <t>Drag and Drop Upload Zone for 100MB MP4 Files</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Verify file picker button opens native OS file selector dialog</t>
+          <t>File Picker OS Dialog Launch Button Action</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -16159,7 +16159,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Verify error message when uploading unsupported file format (.txt, .exe)</t>
+          <t>Unsupported Extension (.exe/.txt) Error Block</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Verify error message when uploading video file exceeding 100MB limit</t>
+          <t>File Size Exceeded (&gt;100MB) Rejection Alert</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Verify posture analysis video upload progress bar updates from 0% to 100%</t>
+          <t>Video Upload Percentage Progress Bar Indicator</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Verify video upload cancellation button aborts file upload HTTP request</t>
+          <t>Upload Cancellation HTTP Request Abort Action</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Verify uploaded video frame extraction process status indicator</t>
+          <t>Frame Extraction Progress Status Spinner Screen</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Verify posture analysis processing screen displays MediaPipe processing spinner</t>
+          <t>AI Video Posture Processing Pipeline Indicator</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Verify video posture analysis completion displays detailed AI report</t>
+          <t>Video AI Analysis Report Generation Render</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Verify posture angle timeline overlay rendered under video player</t>
+          <t>Posture Angle Timeline Video Player Overlay</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Verify video playback controls (Play, Pause, Seek, Speed 0.5x-2x)</t>
+          <t>Video Player Playback Speed Controls (0.5x-2x)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Verify video frame-by-frame step forward button during AI review</t>
+          <t>Video Frame Step Forward Precision Controls</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Verify video frame-by-frame step backward button during AI review</t>
+          <t>Video Frame Step Backward Precision Controls</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Verify Cloudinary image upload for user avatar profile picture</t>
+          <t>Cloudinary Profile Avatar Photo Upload Action</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Verify Cloudinary image cropping modal preview before saving avatar</t>
+          <t>Avatar Image Crop Modal Preview and Adjustment</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Verify invalid image file upload rejection on avatar update</t>
+          <t>Corrupted Image File Upload Failure Rejection</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Verify concurrent file upload handling queue (max 3 files)</t>
+          <t>Parallel File Upload Queue Management (Max 3)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Verify server-side malware virus scan validation on uploaded media</t>
+          <t>Server Anti-Virus Security Scan Validation</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Verify automatic video thumbnail generation post-upload</t>
+          <t>Auto Video Keyframe Thumbnail Generation Test</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Verify posture video analysis report export to PDF</t>
+          <t>Video Posture Evaluation PDF Download Button</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Verify uploaded file deletion button purges file from Cloudinary/S3</t>
+          <t>Uploaded Video File Permanent Deletion Action</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -16767,7 +16767,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Verify video analysis retry button on network transmission failure</t>
+          <t>Network Interruption Upload Retry Action Handler</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Verify video posture summary keyframe highlights gallery display</t>
+          <t>Video Keyframe Highlight Gallery Thumbnail Strip</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Verify video upload bandwidth throttling graceful degraded UX</t>
+          <t>Low Upload Bandwidth Degradation Graceful Mode</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Verify uploaded video aspect ratio preservation in HTML5 video tag</t>
+          <t>Aspect Ratio Preservation in HTML5 Video Tag</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Verify PDF posture evaluation report layout and header formatting</t>
+          <t>PDF Posture Evaluation Report Layout Structure</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Verify PDF report includes user name, date range, and posture grade</t>
+          <t>PDF Report Header User Identity Metadata Render</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Verify PDF report embedded posture score trend chart image quality</t>
+          <t>PDF Report Embedded Trend Chart Image Clarity</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Verify PDF report ergonomic recommendations summary section</t>
+          <t>PDF Ergonomic Recommendation Summary Section</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Verify Excel raw posture telemetry export contains all 33 landmark columns</t>
+          <t>Excel 33 Pose Landmark Raw Coordinates Export</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -17055,7 +17055,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Verify Excel report includes multi-sheet tabs for Sessions, Summary, and Errors</t>
+          <t>Excel Workbook Multi-Sheet Tab Schema Structure</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Verify CSV export file formatting with comma separation and UTF-8 encoding</t>
+          <t>CSV UTF-8 Formatted Data File Dispatch Action</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Verify posture report email delivery feature sends PDF attachment</t>
+          <t>PDF Posture Report Email Delivery Dispatch</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Verify custom date range filter applies to exported report data</t>
+          <t>Date Range Filter Application on Exported Data</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -17183,7 +17183,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Verify automated weekly posture summary report email scheduling</t>
+          <t>Weekly Automated Email Report Schedule Setup</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Verify automated monthly posture summary report email scheduling</t>
+          <t>Monthly Automated Email Report Schedule Setup</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Verify report generation loading overlay during PDF rendering</t>
+          <t>Report PDF Generation Rendering Loading Overlay</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -17279,7 +17279,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Verify print stylesheet (@media print) formats report page cleanly</t>
+          <t>@media print Print Stylesheet Layout Optimizer</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Verify posture health certificate download feature</t>
+          <t>Posture Health Certification PDF Certificate</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Verify posture data anonymized export for medical study consent</t>
+          <t>Anonymized Posture Medical Consent Export Action</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Verify report download failure retry prompt display</t>
+          <t>Report Download Error Retry Action Button Prompt</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Verify password-protected PDF report export security option</t>
+          <t>Password-Encrypted PDF Report Protection Toggle</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Verify corporate team posture aggregation report export for admins</t>
+          <t>Corporate Team Aggregated Posture Admin Report</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Verify export filename includes timestamp (e.g., Posture_Report_20260805.pdf)</t>
+          <t>Report Filename Timestamp Generator Syntax</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Verify top navigation bar links (Home, Calibration, Analytics, Reports, Settings)</t>
+          <t>Top Navbar Primary Destinations Routing Test</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Verify active page route link highlighting in navbar</t>
+          <t>Active Page Link CSS State Highlight Visual</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Verify sidebar toggle button expands and collapses side menu panel</t>
+          <t>Sidebar Collapsible Panel Toggle Button Action</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Verify sidebar navigation links match top navbar destinations</t>
+          <t>Sidebar Navigation Link Destination Matching</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Verify browser back button returns to previously visited route</t>
+          <t>Browser History Back Button Route Reversion</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -17663,7 +17663,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Verify browser forward button navigates ahead correctly</t>
+          <t>Browser History Forward Navigation Flow Test</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Verify browser page refresh (F5) maintains current URL state and session</t>
+          <t>Page Refresh (F5) URL State and Session Retention</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Verify 404 Page Not Found rendering for non-existent URL routes</t>
+          <t>404 Page Not Found Route Fallback Display</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Verify 404 page 'Return to Home' CTA button functionality</t>
+          <t>404 Page 'Return to Dashboard' Button Redirect</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Verify breadcrumbs trail updating dynamically per nested sub-route</t>
+          <t>Dynamic Breadcrumbs Trail Update per Sub-Route</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Verify footer quick links (About, Terms, Privacy, Support, API Docs)</t>
+          <t>Footer Terms and Privacy Policy Hyperlinks</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Verify sticky navigation bar remains pinned to top on page scroll</t>
+          <t>Sticky Navigation Bar Scroll Pinning Behavior</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Verify user profile dropdown menu opens on avatar click</t>
+          <t>User Profile Avatar Header Menu Dropdown Open</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Verify user profile dropdown items (Profile, Billing, Settings, Logout)</t>
+          <t>Profile Dropdown Menu Option Redirects Test</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Verify keyboard shortcut 'G+D' navigates to Dashboard</t>
+          <t>Keyboard Shortcut 'G+D' Dashboard Navigation</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Verify keyboard shortcut 'G+C' navigates to Calibration</t>
+          <t>Keyboard Shortcut 'G+C' Calibration Navigation</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Verify modal dialog close button (X) dismisses overlay</t>
+          <t>Modal Close Button (X) Click Dismiss Action</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -18047,7 +18047,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Verify pressing ESC key closes open modal dialogs</t>
+          <t>Escape Key Press Modal Window Dismissal</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Verify clicking outside modal backdrop dismisses overlay</t>
+          <t>Backdrop Click Modal Dismissal Behavior Test</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Verify page title (&lt;title&gt; tag) updates dynamically per route</t>
+          <t>Dynamic Page Document Title (&lt;title&gt;) Updates</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Verify dark mode theme toggle switches CSS background and text variables</t>
+          <t>Dark Theme Palette Variable CSS Class Switch</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -18175,7 +18175,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Verify light mode theme toggle restores original high-contrast theme</t>
+          <t>Light Theme High-Contrast Mode Color Restoration</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -18207,7 +18207,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Verify system color scheme preference (prefers-color-scheme) auto-detection</t>
+          <t>System Prefers-Color-Scheme Auto Detection</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Verify persistent theme preference saved in browser localStorage</t>
+          <t>Theme Preference Persistence in localStorage</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Verify high contrast mode toggle for visually impaired users</t>
+          <t>High Contrast Accessibility Toggle Switch</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Verify font size scaling controls (Small, Medium, Large, Extra Large)</t>
+          <t>Typography Font Size Scaling (Small to XL)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Verify screen reader ARIA labels on all interactive buttons</t>
+          <t>Interactive Component Screen Reader ARIA Labels</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Verify ARIA live regions announce posture status changes</t>
+          <t>ARIA Live Region Speech Output on Alert Push</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -18399,7 +18399,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Verify keyboard focus indicator outline visible on TAB navigation</t>
+          <t>Keyboard TAB Focus Outline Indicator Highlight</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Verify tab order traverses web page elements in logical reading sequence</t>
+          <t>Logical TAB Key Navigation Order Sequence</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Verify color contrast ratio meets WCAG 2.1 AA benchmark (4.5:1 ratio)</t>
+          <t>WCAG 2.1 AA Color Contrast Ratio Verification</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -18495,7 +18495,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Verify form input fields have explicit associated &lt;label&gt; elements</t>
+          <t>Form Input Field Associated &lt;label&gt; Tag Check</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -18527,7 +18527,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Verify decorative images have empty alt text (alt='')</t>
+          <t>Decorative Image Empty Alt Text (alt='') Rule</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -18559,7 +18559,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Verify functional images have descriptive alt text</t>
+          <t>Functional Icon Graphic Descriptive Alt Text</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Verify skipping to main content link works for screen readers</t>
+          <t>'Skip to Main Content' Accessibility Link Test</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Verify interface animations pause when prefers-reduced-motion is active</t>
+          <t>Prefers-Reduced-Motion CSS Transition Freeze</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Verify tooltips accessible via keyboard focus hover</t>
+          <t>Keyboard Focus Hover Tooltip Popover Action</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Verify error state text is not conveyed by color alone (includes icons)</t>
+          <t>Multi-Sensory Error State Display (Icon plus Text)</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -18719,7 +18719,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Verify language attribute (&lt;html lang='en'&gt;) defined on document root</t>
+          <t>Document Root Language Attribute (&lt;html lang='en'&gt;)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -18751,7 +18751,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Verify semantic HTML5 tags (&lt;header&gt;, &lt;main&gt;, &lt;nav&gt;, &lt;footer&gt;) used throughout</t>
+          <t>Semantic HTML5 Structural Tags Layout Integrity</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Verify user profile name field trims leading and trailing whitespace</t>
+          <t>User Profile Display Name Whitespace Trimming</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Verify user profile name field max length restriction (50 chars)</t>
+          <t>Profile Display Name Character Cap (50 Chars)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Verify special character handling in user profile display name</t>
+          <t>Special Character Encoding in User Display Name</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Verify email input field auto-complete attribute enabled</t>
+          <t>Email Address Field Browser Autocomplete Attribute</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Verify birthdate date picker restricts selection of future dates</t>
+          <t>Birthdate Selection Future Date Rejection Rule</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Verify height/weight numeric input fields reject negative numbers</t>
+          <t>Height and Weight Input Field Negative Number Rejection</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Verify height metric (cm) vs imperial (inches) unit toggle calculation</t>
+          <t>Height Units Switcher (Centimeters vs Inches)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Verify weight metric (kg) vs imperial (lbs) unit toggle calculation</t>
+          <t>Weight Units Switcher (Kilograms vs Pounds)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Verify posture target daily goal input field (range 15 to 480 mins)</t>
+          <t>Daily Posture Target Goal Range (15-480 Mins)</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Verify real-time inline validation error display on blur event</t>
+          <t>Inline Real-Time Input Error Blur Validation</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Verify submit button disabled until all mandatory form fields are valid</t>
+          <t>Submit Button Disabled State on Invalid Inputs</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Verify clearing form button resets input fields to default values</t>
+          <t>Form Reset Clear Button Default State Restore</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -19167,7 +19167,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Verify unsaved form changes warning modal on navigating away</t>
+          <t>Unsaved Form Changes Warning Navigation Alert</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Verify HTML form submission triggers on pressing Enter key inside text input</t>
+          <t>Enter Key Press Form Submission Event Launch</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -19231,7 +19231,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Verify text area character counter updates live as user types</t>
+          <t>Textarea Live Remaining Character Counter</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Verify password confirmation field matches new password input</t>
+          <t>Password Confirmation Match Validation Check</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Verify SQL injection string in input field is escaped properly</t>
+          <t>Input Escaping Security against SQL Injection</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Verify HTML code snippet input is escaped to prevent XSS execution</t>
+          <t>HTML Tag Encoding Security against XSS Payloads</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Verify form submission double-click prevention disables submit button</t>
+          <t>Submit Button Double-Click Action Prevention</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Verify desktop layout rendering at 1920x1080 resolution</t>
+          <t>1920x1080 Full HD Monitor Viewport Layout</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Verify laptop layout rendering at 1366x768 resolution</t>
+          <t>1366x768 Standard Laptop Monitor Viewport Layout</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Verify tablet viewport rendering at 768x1024 portrait resolution</t>
+          <t>768x1024 Tablet Portrait Mode Viewport Layout</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Verify mobile viewport rendering at 375x812 iPhone X resolution</t>
+          <t>375x812 iPhone Mobile Screen Viewport Layout</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Verify hamburger menu appears on screens below 768px width</t>
+          <t>Mobile Viewport Hamburger Navigation Menu Appears</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Verify navigation menu collapses into slide-over drawer on mobile</t>
+          <t>Mobile Side-Drawer Navigation Transition</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Verify dashboard analytics grid wraps from 4 columns to 1 column on mobile</t>
+          <t>Dashboard 4-Column Grid Collapse to 1-Column</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Verify live video stream canvas scales proportionally to screen width</t>
+          <t>Webcam Live Canvas Fluid Width Resizing</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Verify data tables horizontal scrollbar display on small viewports</t>
+          <t>Data Table Horizontal Scroll Bar Mobile Rendering</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Verify touch drag gestures supported on mobile charts slider</t>
+          <t>Touch Screen Drag Gesture Support on Charts</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Verify Chrome browser latest version rendering stability</t>
+          <t>Google Chrome Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Verify Firefox browser latest version rendering stability</t>
+          <t>Mozilla Firefox Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -19775,7 +19775,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Verify Safari browser latest version rendering stability</t>
+          <t>Apple Safari Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Verify Microsoft Edge browser latest version rendering stability</t>
+          <t>Microsoft Edge Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Verify MediaPipe WASM module loading across Chromium and WebKit browsers</t>
+          <t>MediaPipe WASM Engine Cross-Browser Loading</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -19871,7 +19871,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Verify WebGL 2.0 context initialization fallback on legacy hardware</t>
+          <t>WebGL Context Initialization Hardware Fallback</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Verify high DPI Retina display crisp image rendering</t>
+          <t>High DPI Retina Display Image Sharpness Check</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -19935,7 +19935,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Verify viewport meta tag (width=device-width, initial-scale=1.0) present</t>
+          <t>Viewport Meta Tag Initial Scale Configuration</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Verify page content does not cause unintended horizontal overflow</t>
+          <t>Zero Horizontal Page Overflow Layout Inspection</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -19999,7 +19999,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Verify CSS grid and flexbox layout stability across browser engines</t>
+          <t>CSS Grid and Flexbox Layout Engine Parity</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Verify touch target minimum size of 44x44 pixels on mobile viewports</t>
+          <t>Minimum 44x44px Touch Target Size Verification</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Verify smooth CSS transition animations at 60 FPS</t>
+          <t>CSS Smooth Transition Animation 60 FPS Check</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -20095,7 +20095,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Verify print CSS media query removes background images and navigation bars</t>
+          <t>@media print Navigation and Header Masking</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Verify web app manifest (manifest.json) PWA installability prompt</t>
+          <t>Web App Manifest PWA Installability Prompt</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -20210,7 +20210,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify CSRF token validation on POST form submissions</t>
+          <t>CSRF Security Token Validation on POST Actions</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify CSRF token validation on POST form submissions' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'CSRF Security Token Validation on POST Actions' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20247,7 +20247,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify live slouch counter increments when slouch duration exceeds 5s</t>
+          <t>Slouch Event Counter Trigger on 5s Continuous Slouch</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify live slouch counter increments when slouch duration exceeds 5s' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Slouch Event Counter Trigger on 5s Continuous Slouch' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify dashboard chart image export to PNG button</t>
+          <t>Chart Vector Image PNG Export Trigger Button</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20304,7 +20304,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify dashboard chart image export to PNG button' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Chart Vector Image PNG Export Trigger Button' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify mark all notifications as read button updates UI badge</t>
+          <t>Mark All Notifications as Read Action Button</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify mark all notifications as read button updates UI badge' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Mark All Notifications as Read Action Button' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20358,7 +20358,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify report preview modal displays accurate multi-page preview</t>
+          <t>Multi-Page Report Preview Dialog Modal Render</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify report preview modal displays accurate multi-page preview' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Multi-Page Report Preview Dialog Modal Render' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify phone number field enforces international E.164 format (+1234567890)</t>
+          <t>E.164 International Phone Format Validation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20415,7 +20415,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify phone number field enforces international E.164 format (+1234567890)' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'E.164 International Phone Format Validation' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20432,7 +20432,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify font size scaling dynamically across desktop, tablet, and mobile breakpoints</t>
+          <t>Fluid Typography Clamp Font Size Scaling</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20452,7 +20452,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify font size scaling dynamically across desktop, tablet, and mobile breakpoints' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Fluid Typography Clamp Font Size Scaling' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20646,7 +20646,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify CSRF token validation on POST form submissions' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'CSRF Security Token Validation on POST Actions' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20668,7 +20668,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify live slouch counter increments when slouch duration exceeds 5s' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Slouch Event Counter Trigger on 5s Continuous Slouch' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20690,7 +20690,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify dashboard chart image export to PNG button' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Chart Vector Image PNG Export Trigger Button' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify mark all notifications as read button updates UI badge' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Mark All Notifications as Read Action Button' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify report preview modal displays accurate multi-page preview' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Multi-Page Report Preview Dialog Modal Render' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20756,7 +20756,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify phone number field enforces international E.164 format (+1234567890)' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'E.164 International Phone Format Validation' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify font size scaling dynamically across desktop, tablet, and mobile breakpoints' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Fluid Typography Clamp Font Size Scaling' failed visual tolerance check</t>
         </is>
       </c>
     </row>
